--- a/Current TAPPs/EPMA_TAPP_v25.xlsx
+++ b/Current TAPPs/EPMA_TAPP_v25.xlsx
@@ -5393,7 +5393,7 @@
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>Numeric (um)</t>
+          <t>Numeric (µm)</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>Numeric pair (um x um)</t>
+          <t>Numeric pair (µm x µm)</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>Numeric (um)</t>
+          <t>Numeric (µm)</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>Numeric pair (um x um)</t>
+          <t>Numeric pair (µm x µm)</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
